--- a/healthcare_assessment_forms/010_integrative_health_assessment--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/010_integrative_health_assessment--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_blood_pressure'}</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High blood pressure'}</t>
+          <t>High blood pressure</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'heart_disease'}</t>
+          <t>heart_disease</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Heart disease'}</t>
+          <t>Heart disease</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'options':_[]}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'options': []}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general_health'}</t>
+          <t>general_health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'General health'}</t>
+          <t>General health</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weight_loss'}</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weight loss'}</t>
+          <t>Weight loss</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'stress_management'}</t>
+          <t>stress_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Stress management'}</t>
+          <t>Stress management</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'sleep'}</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Sleep'}</t>
+          <t>Sleep</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'spiritual_growth'}</t>
+          <t>spiritual_growth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Spiritual growth'}</t>
+          <t>Spiritual growth</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'nutrition'}</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Nutrition'}</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'mindfulness'}</t>
+          <t>mindfulness</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Mindfulness'}</t>
+          <t>Mindfulness</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'group'}</t>
+          <t>group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Group'}</t>
+          <t>Group</t>
         </is>
       </c>
     </row>
